--- a/output/pdf_financials_xlsx/UIG.xlsx
+++ b/output/pdf_financials_xlsx/UIG.xlsx
@@ -808,10 +808,10 @@
         <v>-0.112568</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.084915</v>
+        <v>-0.084915</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.166022</v>
+        <v>-0.166022</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         <v>-0.112568</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.084915</v>
+        <v>-0.084915</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.166022</v>
+        <v>-0.166022</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
         <v>-0.112568</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.084915</v>
+        <v>-0.084915</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.166022</v>
+        <v>-0.166022</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>8.3011</v>
+        <v>-8.3011</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         <v>-0.112568</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.084915</v>
+        <v>-0.084915</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.166022</v>
+        <v>-0.166022</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         <v>-0.112568</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.084915</v>
+        <v>-0.084915</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.166022</v>
+        <v>-0.166022</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1218,10 +1218,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.119566</v>
+        <v>0.005</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.09193</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="49">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.084915</v>
+        <v>-0.084915</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.166022</v>
+        <v>-0.166022</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -7842,10 +7842,10 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0.112568</v>
+        <v>-0.112568</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.084915</v>
+        <v>-0.084915</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/UIG.xlsx
+++ b/output/pdf_financials_xlsx/UIG.xlsx
@@ -1280,19 +1280,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.370736</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.297287</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.132115</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.67198</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.6691859999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1324,19 +1324,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.370736</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.297287</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.132115</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.67198</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.6691859999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1597,10 +1597,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.005</v>
+        <v>0.447586</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.005</v>
+        <v>0.422744</v>
       </c>
     </row>
     <row r="49">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">

--- a/output/pdf_financials_xlsx/UIG.xlsx
+++ b/output/pdf_financials_xlsx/UIG.xlsx
@@ -501,15 +501,11 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="3" t="n">
+        <v>5.381874</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5.06446</v>
       </c>
     </row>
     <row r="5">
@@ -527,15 +523,11 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>4.344689</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>4.170098</v>
       </c>
     </row>
     <row r="6">
@@ -553,15 +545,11 @@
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="3" t="n">
+        <v>1.037185</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.894362</v>
       </c>
     </row>
     <row r="7">
@@ -579,15 +567,11 @@
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="3" t="n">
+        <v>0.390979</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.426194</v>
       </c>
     </row>
     <row r="8">
@@ -605,15 +589,11 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -631,15 +611,11 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -657,15 +633,11 @@
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="3" t="n">
+        <v>1.999471</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2.24308</v>
       </c>
     </row>
     <row r="11">
@@ -683,15 +655,11 @@
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="3" t="n">
+        <v>-0.962286</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-1.348718</v>
       </c>
     </row>
     <row r="12">
@@ -709,15 +677,11 @@
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -735,15 +699,11 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -761,15 +721,11 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -787,15 +743,11 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>0.006762</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.014702</v>
       </c>
     </row>
     <row r="16">
@@ -813,15 +765,11 @@
       <c r="D16" s="3" t="n">
         <v>-0.166022</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>-2.523322</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-1.5314</v>
       </c>
     </row>
     <row r="17">
@@ -839,15 +787,11 @@
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -929,15 +873,11 @@
       <c r="D20" s="3" t="n">
         <v>-0.166022</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-2.523322</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-1.5314</v>
       </c>
     </row>
     <row r="21">
@@ -955,15 +895,11 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -981,15 +917,11 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1007,15 +939,11 @@
       <c r="D23" s="3" t="n">
         <v>-0.166022</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="3" t="n">
+        <v>-2.523322</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-1.5314</v>
       </c>
     </row>
     <row r="24">
@@ -1113,15 +1041,11 @@
       <c r="D27" s="3" t="n">
         <v>-0.166022</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>-2.523322</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-1.5314</v>
       </c>
     </row>
     <row r="28">
@@ -1139,15 +1063,11 @@
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0.112941</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.09118800000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1165,15 +1085,11 @@
       <c r="D29" s="3" t="n">
         <v>-0.166022</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>-2.410381</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-1.440212</v>
       </c>
     </row>
     <row r="30">
@@ -1197,15 +1113,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E30" s="3" t="n">
+        <v>-44.78702028326936</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>-28.43762217492092</v>
       </c>
     </row>
     <row r="31">
@@ -1223,15 +1135,11 @@
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1255,15 +1163,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E32" s="3" t="n">
+        <v>-46.88556439634224</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>-30.23816951856664</v>
       </c>
     </row>
     <row r="33">
@@ -2034,13 +1938,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.067318</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.09136</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.19831</v>
       </c>
     </row>
     <row r="68">
@@ -2059,10 +1963,10 @@
         <v>0.029309</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.538117</v>
+        <v>0.629477</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1.030159</v>
+        <v>1.228469</v>
       </c>
     </row>
     <row r="69">
@@ -2103,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.017936</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.01952</v>
       </c>
     </row>
     <row r="71">
@@ -2125,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.017936</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.01952</v>
       </c>
     </row>
     <row r="72">
@@ -2213,10 +2117,10 @@
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.356359</v>
+        <v>0.247063</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.703062</v>
+        <v>0.485232</v>
       </c>
     </row>
     <row r="76">
@@ -2335,10 +2239,10 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.0151300443759816</v>
+        <v>0.02496238046031515</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.01085827399134295</v>
+        <v>0.03709014383181501</v>
       </c>
     </row>
     <row r="81">
@@ -2771,15 +2675,11 @@
       <c r="D99" s="3" t="n">
         <v>-0.166022</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="3" t="n">
+        <v>-2.523322</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-1.5314</v>
       </c>
     </row>
     <row r="100">
@@ -2797,15 +2697,11 @@
       <c r="D100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="3" t="n">
+        <v>0.112941</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0.09118800000000001</v>
       </c>
     </row>
     <row r="101">
@@ -2823,15 +2719,11 @@
       <c r="D101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="3" t="n">
+        <v>0.522064</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>-0.029988</v>
       </c>
     </row>
     <row r="102">
@@ -2849,15 +2741,11 @@
       <c r="D102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2875,15 +2763,11 @@
       <c r="D103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2901,15 +2785,11 @@
       <c r="D104" s="3" t="n">
         <v>0.00085</v>
       </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" s="3" t="n">
+        <v>-0.391726</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0.492042</v>
       </c>
     </row>
     <row r="105">
@@ -2927,15 +2807,11 @@
       <c r="D105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2953,15 +2829,11 @@
       <c r="D106" s="3" t="n">
         <v>-0.165172</v>
       </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="3" t="n">
+        <v>0.125338</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0.462054</v>
       </c>
     </row>
     <row r="107">
@@ -2979,15 +2851,11 @@
       <c r="D107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="3" t="n">
+        <v>0.14042</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0.410348</v>
       </c>
     </row>
     <row r="108">
@@ -3005,15 +2873,11 @@
       <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3031,15 +2895,11 @@
       <c r="D109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3057,15 +2917,11 @@
       <c r="D110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3083,15 +2939,11 @@
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E111" s="3" t="n">
+        <v>-0.254171</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>-0.003985</v>
       </c>
     </row>
     <row r="112">
@@ -3109,15 +2961,11 @@
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3135,15 +2983,11 @@
       <c r="D113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3161,15 +3005,11 @@
       <c r="D114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3187,15 +3027,11 @@
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3213,15 +3049,11 @@
       <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3239,15 +3071,11 @@
       <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3265,15 +3093,11 @@
       <c r="D118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3297,15 +3121,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E119" s="3" t="n">
+        <v>-0.020831</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>-0.003985</v>
       </c>
     </row>
     <row r="120">
@@ -3323,15 +3143,11 @@
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0.041</v>
       </c>
     </row>
     <row r="121">
@@ -3349,15 +3165,11 @@
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3375,15 +3187,11 @@
       <c r="D122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3401,15 +3209,11 @@
       <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3427,15 +3231,11 @@
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3453,15 +3253,11 @@
       <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3479,15 +3275,11 @@
       <c r="D126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E126" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3537,15 +3329,11 @@
       <c r="D128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="3" t="n">
+        <v>1.29186</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3569,15 +3357,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" s="3" t="n">
+        <v>0.648238</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>0.580156</v>
       </c>
     </row>
     <row r="130">
@@ -3601,15 +3385,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E130" s="3" t="n">
+        <v>0.951197</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.67198</v>
       </c>
     </row>
     <row r="131">
@@ -3627,15 +3407,11 @@
       <c r="D131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3653,15 +3429,11 @@
       <c r="D132" s="3" t="n">
         <v>-0.165172</v>
       </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E132" s="3" t="n">
+        <v>-0.279217</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-0.002794</v>
       </c>
     </row>
     <row r="133">
@@ -3685,15 +3457,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E133" s="3" t="n">
+        <v>0.67198</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0.6691859999999999</v>
       </c>
     </row>
     <row r="134">
@@ -3711,15 +3479,11 @@
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="3" t="n">
+        <v>-0.254171</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>-0.003985</v>
       </c>
     </row>
     <row r="135">
@@ -3743,15 +3507,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E135" s="3" t="n">
+        <v>-1.160795</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>-0.58295</v>
       </c>
     </row>
   </sheetData>
@@ -3765,7 +3525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4419,7 +4179,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -5669,7 +5433,11 @@
           <t>Lease liabilities 9 17,936</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -6809,14 +6577,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>OPERATING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6824,24 +6588,26 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E74" s="5" t="n">
-        <v>-0.112568</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>-0.084915</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>-0.166022</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>-2.523322</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>-1.5314</v>
       </c>
     </row>
     <row r="75">
@@ -6852,37 +6618,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Increase in accounts payable and accrued liabilities</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>0.016993</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0.011466</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>0.00085</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.112941</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0.09118800000000001</v>
       </c>
     </row>
     <row r="76">
@@ -6893,37 +6661,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital total</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>-0.047674</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>-0.073449</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>-0.165172</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0.14042</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>0.410348</v>
       </c>
     </row>
     <row r="77">
@@ -6934,34 +6704,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Change in cash</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Non-cash listing costs</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F77" s="5" t="n">
-        <v>-0.073449</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>-0.165172</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>1.788718</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6977,35 +6745,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Opening cash</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Deferred tax</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F78" s="5" t="n">
-        <v>0.370736</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>0.297287</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>-0.426</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>0.129</v>
       </c>
     </row>
     <row r="79">
@@ -7016,12 +6788,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Closing cash $</t>
+          <t>Bad debts</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -7030,21 +6802,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>0.297287</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>0.132115</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0.010579</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0.024526</v>
       </c>
     </row>
     <row r="80">
@@ -7055,12 +6827,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Description of the Business</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>related conditions of a "Qualifying Transaction" (“QT”) under the Exchange rules. on April</t>
+          <t>Finance expenses</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -7069,21 +6841,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>2.6e-05</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="5" t="n">
+        <v>0.023155</v>
       </c>
     </row>
     <row r="81">
@@ -7094,30 +6868,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Period from</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Gain from disposition of assets</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>1.1e-05</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H81" s="5" t="n">
+        <v>-0.009457</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7133,21 +6909,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>0.047901</v>
+          <t>CEBA Loan</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7159,10 +6933,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H82" s="5" t="n">
+        <v>-0.01</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7178,21 +6950,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Issuance of common shares</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>0.41841</v>
+          <t>Cash flows - operating activities before working capital changes</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7204,15 +6974,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H83" s="5" t="n">
+        <v>-0.916121</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>-0.853183</v>
       </c>
     </row>
     <row r="84">
@@ -7223,39 +6989,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Changes in</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Trade and other receivables</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>0.370736</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>-0.073449</v>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H84" s="5" t="n">
+        <v>0.522064</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>-0.029988</v>
       </c>
     </row>
     <row r="85">
@@ -7266,12 +7032,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Changes in</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Opening cash</t>
+          <t>Holdback receivables</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -7280,23 +7046,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>0.370736</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H85" s="5" t="n">
+        <v>0.085297</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>0.039682</v>
       </c>
     </row>
     <row r="86">
@@ -7307,35 +7071,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Changes in</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Closing cash $</t>
+          <t>Contract assets</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>0.370736</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>0.297287</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H86" s="5" t="n">
+        <v>0.116365</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>-0.027066</v>
       </c>
     </row>
     <row r="87">
@@ -7346,134 +7110,140 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>"Qualifying Transaction" (“QT”) under the Exchange rules.</t>
+          <t>Changes in</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>The address of the Company’s registered office is Suite 2100, 40 King Street West, Toronto, Ontario, M5H 3C2. on March</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>Trade and other payables</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H87" s="5" t="n">
+        <v>-0.391726</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0.492042</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Regulatory and listing costs $</t>
+          <t>Other liabilities</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>0.020532</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>0.012625</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>0.034782</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>-0.046194</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>-0.0194</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>0.044135</v>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>0.07228999999999999</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>0.13124</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Tax liabilities</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>-0.276309</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>-0.181052</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Changes in total</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
-        <v>0.047901</v>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7485,36 +7255,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H90" s="5" t="n">
+        <v>0.009497999999999999</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>0.274218</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS FOR THE YEAR</t>
+          <t>Net cash from / (used in) operating activities</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7522,98 +7288,102 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>-0.084915</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.166022</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>-0.906624</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>-0.578965</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash flows from / (used in) investing activities</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NET LOSS PER SHARE – Basic and diluted $</t>
+          <t>Acquisition of property, plant, and equipment</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>2e-08</v>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="5" t="n">
+        <v>-0.003985</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash flows from / (used in) investing activities</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING – Basic</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>6.18381</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>8.207001</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>8.207001</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Down payment on acquisition of right of use assets</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>-0.020831</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -7624,138 +7394,146 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Shares       Shares     Warrants</t>
+          <t>Cash flows from / (used in) investing activities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Balance, January 1, 2022 8,207,001 $ 405,188 $ 13,222 $ 47,901 $</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Net cash from / (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>0.353743</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.112568</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-0.020831</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>-0.003985</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Shares       Shares     Warrants</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Proceeds from borrowings</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F95" s="5" t="n">
-        <v>-0.084915</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>-0.084915</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="5" t="n">
+        <v>0.04064</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Shares       Shares     Warrants</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 8,207,001 405,188 13,222 47,901</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Proceeds from exercise of options</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F96" s="5" t="n">
-        <v>0.268828</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>-0.197483</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="5" t="n">
+        <v>0.041</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Shares       Shares     Warrants</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 8,207,001 $ 405,188 $ 13,222 $ 47,901 $</t>
+          <t>Proceeds from related party loans</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7764,55 +7542,63 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F97" s="5" t="n">
-        <v>0.102806</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>-0.363505</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="5" t="n">
+        <v>0.516452</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Period from</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>June</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>1.1e-05</v>
+          <t>Issuance of shares, net of share issue costs</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H98" s="5" t="n">
+        <v>1.29186</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7823,39 +7609,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS FOR THE PERIOD</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="n">
-        <v>-0.112568</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>-0.084915</v>
+          <t>Repayment of borrowings</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H99" s="5" t="n">
+        <v>-0.125513</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7866,17 +7650,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shares       Shares     Warrants</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Balance, June 11, 2021 - $ - $ - $ - $</t>
+          <t>Payment of lease liabilities</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7895,36 +7679,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H100" s="5" t="n">
+        <v>-0.018109</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>-0.017936</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Shares       Shares     Warrants</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - 47,901</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" s="5" t="n">
-        <v>0.047901</v>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -7936,10 +7722,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H101" s="5" t="n">
+        <v>-0.5</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7950,22 +7734,28 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Shares       Shares     Warrants</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Private placement for cash 5,700,001 285,000 -</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" s="5" t="n">
-        <v>0.285</v>
+          <t>Net cash from / (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -7977,36 +7767,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H102" s="5" t="n">
+        <v>0.648238</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>0.580156</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Shares       Shares     Warrants</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Issuance of common shares 2,507,000 120,188 13,222 -</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" s="5" t="n">
-        <v>0.13341</v>
+          <t>Net increase / (decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8018,131 +7810,129 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H103" s="5" t="n">
+        <v>-0.279217</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>-0.002794</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>for cash</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Net loss for the period - - - -</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>-0.112568</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>-0.112568</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H104" s="5" t="n">
+        <v>0.951197</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.67198</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>for cash</t>
+          <t>Cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 8,207,001 405,188 13,222 47,901</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" s="5" t="n">
-        <v>0.353743</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>-0.112568</v>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H105" s="5" t="n">
+        <v>0.67198</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>0.6691859999999999</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>for cash</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Balance, January 1, 2022 8,207,001 405,188 13,222 47,901</t>
+          <t>Profit (loss) for the period $ (2,523,322) $</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" s="5" t="n">
-        <v>0.353743</v>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>-0.112568</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H106" s="5" t="n">
+        <v>1.647887</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -8153,39 +7943,41 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>for cash</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
+          <t>Depreciation and amortization 112,941</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="n">
-        <v>-0.084915</v>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>-0.084915</v>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H107" s="5" t="n">
+        <v>0.097387</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -8196,37 +7988,4880 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Share-based payments 140,420</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Non-cash Listing costs 1,788,718</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tax expense (recovery) (426,000)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>0.462128</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Bad debts 10,579</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0.007019</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Net finance (income) / expense 3,757</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>0.001031</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Loss (gain) on disposition of assets (9,457)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>-0.006265</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CEBA loan (10,000)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Cash flow - operating activities before working capital changes (912,364)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>2.209187</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Trade and other receivables 522,064</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>-0.6193959999999999</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Holdback receivables 85,297</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>-0.146705</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Prepaid expenses and other current assets -</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Contract assets 116,365</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>0.126295</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Trade and other payables (391,725)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>-0.09604600000000001</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Due to related party -</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>-0.121451</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Other liabilities (46,194)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>-0.08065899999999999</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tax liabilities (276,309)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Changes in</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Net cash from (used in) operating activities (902,866)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>1.266225</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Cash flows - investing activities</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Net acquisition of property, plant, and equipment -</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>-0.254171</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cash flows - investing activities</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Down payment on acquisition of right of use assets (20,831)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Cash flows - investing activities</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Net cash from (used in) investing activities (20,831)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>-0.254171</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Payment of lease liabilities (21,866)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>-0.015062</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Issuance of shares, net of share issue costs 1,291,860</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Proceeds from borrowings -</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>0.136207</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Repayment of borrowings (125,513)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>-0.09561799999999999</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Dividends paid (500,000)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Net cash from (used in) financing activities 644,481</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>-0.024752</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Net increase (decrease) in cash and cash equivalents (279,217)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>0.987302</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents - beginning of period 951,197</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>-0.036105</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents - end of period $ 671,980 $</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>0.951197</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Cash flows - financing activities</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SUPLEMENTAL CASH FLOW INFORMATION (Note</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>2.4e-05</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>-0.112568</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-0.084915</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>-0.166022</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Change in non-cash working capital</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Increase in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.016993</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>0.011466</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.00085</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Change in non-cash working capital</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Change in non-cash working capital total</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>-0.047674</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>-0.073449</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>-0.165172</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Change in non-cash working capital</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>-0.073449</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>-0.165172</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Change in non-cash working capital</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Opening cash</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>0.370736</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.297287</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Change in non-cash working capital</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Closing cash $</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.297287</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.132115</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Description of the Business</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>related conditions of a "Qualifying Transaction" (“QT”) under the Exchange rules. on April</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>2.6e-05</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Period from</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>1.1e-05</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>0.047901</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>0.41841</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>0.370736</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>-0.073449</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Opening cash</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>0.370736</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Closing cash $</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" s="5" t="n">
+        <v>0.370736</v>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>0.297287</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>"Qualifying Transaction" (“QT”) under the Exchange rules.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>The address of the Company’s registered office is Suite 2100, 40 King Street West, Toronto, Ontario, M5H 3C2. on March</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Revenue 17</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>5.381874</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>5.06446</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Cost of services 18</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>4.344689</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>4.170098</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>1.037185</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>0.894362</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Consulting and management fees 20</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>0.195863</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>0.220692</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Depreciation 8, 9</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>0.112941</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>0.09118800000000001</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Equipment and other</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>0.180822</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>0.105182</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>General and administrative 19</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>0.214547</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>0.357246</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>0.111249</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>0.132863</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>0.0474</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Licenses, due and subscription</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>0.000375</v>
+      </c>
+      <c r="I161" s="5" t="n">
+        <v>0.002587</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Marketing and promotion</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>0.036467</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>0.025239</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>0.283532</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>0.23919</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Remuneration and benefits 20</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>0.6742050000000001</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>0.611145</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Repairs and maintenance</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="n">
+        <v>0.00165</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>0.14042</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>0.410348</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>1.999471</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>2.24308</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Operating profit (loss)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>-0.962286</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>-1.348718</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Finance expenses</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>-0.04106</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>-0.068384</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Listing expenses 4</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>-1.958062</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Other income/expense</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>0.006762</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>0.014702</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Net income (loss) before tax</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>-2.954646</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>-1.4024</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Income tax (expense) / benefit</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Current tax 13</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>0.005324</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Income tax (expense) / benefit</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Deferred tax 13</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>-0.129</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Income tax (expense) / benefit</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Net income (loss) and comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="n">
+        <v>-2.523322</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>-1.5314</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Weighted average number of common share outstanding</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>55.968758</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>104.535383</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Weighted average number of common share outstanding</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="n">
+        <v>55.968758</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>104.535383</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Revenue 17 $ 5,381,874 $</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>12.276877</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Cost of services 18 (4,344,689)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>-8.646496000000001</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Gross margin 1,037,185</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>3.630381</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Consulting fees 34,075</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Depreciation 8,9 112,941</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>0.097387</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Equipment and other 180,822</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>0.223683</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>General and administrative 19 214,547</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>0.176314</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Insurance 111,249</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="n">
+        <v>0.07045800000000001</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Investor Relations 47,400</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Licenses, due and subscription 375</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>0.00908</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Marketing and promotion 36,467</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>0.031771</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Professional fees 445,320</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>0.224259</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Remuneration and benefits 20 674,205</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>0.642451</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Repairs and maintenance 1,650</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>0.001573</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Share-based payments 140,420</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Operating profit (loss) (962,286)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="n">
+        <v>2.153405</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Other Income (Loss)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Finance expenses (41,060)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="n">
+        <v>-0.043442</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Other Income (Loss)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Listing expenses 4 (1,958,062)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Other Income (Loss)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Other income 6,762</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>0.005894</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Other Income (Loss)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Profit (loss) before tax (2,954,646)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>2.115857</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Income tax (expense) / benefit</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Current tax 5,324</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>-0.45697</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Income tax (expense) / benefit</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Deferred tax 426,000</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Income tax (expense) / benefit</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Net profit (loss) and comprehensive income(loss) $ (2,523,322) $</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" s="5" t="n">
+        <v>1.647887</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Earnings (loss) per share</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Basic $ (0.05) $</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="n">
+        <v>0.008239</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Earnings (loss) per share</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Diluted $ (0.05) $</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>0.008239</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Basic 55,968,758</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Diluted 55,968,758</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Regulatory and listing costs $</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="5" t="n">
+        <v>0.020532</v>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>0.012625</v>
+      </c>
+      <c r="G205" s="5" t="n">
+        <v>0.034782</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n">
+        <v>0.044135</v>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>0.07228999999999999</v>
+      </c>
+      <c r="G206" s="5" t="n">
+        <v>0.13124</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>0.047901</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>NET LOSS AND COMPREHENSIVE LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>-0.084915</v>
+      </c>
+      <c r="G208" s="5" t="n">
+        <v>-0.166022</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>NET LOSS PER SHARE – Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="F209" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G209" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING – Basic</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>6.18381</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>8.207001</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>8.207001</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Shares       Shares     Warrants</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Balance, January 1, 2022 8,207,001 $ 405,188 $ 13,222 $ 47,901 $</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>0.353743</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>-0.112568</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Shares       Shares     Warrants</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>-0.084915</v>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>-0.084915</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Shares       Shares     Warrants</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2022 8,207,001 405,188 13,222 47,901</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>0.268828</v>
+      </c>
+      <c r="G213" s="5" t="n">
+        <v>-0.197483</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Shares       Shares     Warrants</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2023 8,207,001 $ 405,188 $ 13,222 $ 47,901 $</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>0.102806</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>-0.363505</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Period from</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>1.1e-05</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>NET LOSS AND COMPREHENSIVE LOSS FOR THE PERIOD</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="n">
+        <v>-0.112568</v>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>-0.084915</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Shares       Shares     Warrants</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Balance, June 11, 2021 - $ - $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Shares       Shares     Warrants</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Share-based compensation - - - 47,901</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" s="5" t="n">
+        <v>0.047901</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Shares       Shares     Warrants</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Private placement for cash 5,700,001 285,000 -</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" s="5" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Shares       Shares     Warrants</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Issuance of common shares 2,507,000 120,188 13,222 -</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" s="5" t="n">
+        <v>0.13341</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
         <is>
           <t>for cash</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Net loss for the period - - - -</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>-0.112568</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>-0.112568</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>for cash</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2021 8,207,001 405,188 13,222 47,901</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" s="5" t="n">
+        <v>0.353743</v>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>-0.112568</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>for cash</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Balance, January 1, 2022 8,207,001 405,188 13,222 47,901</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" s="5" t="n">
+        <v>0.353743</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>-0.112568</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>for cash</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="n">
+        <v>-0.084915</v>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>-0.084915</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>for cash</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>Balance, December 31, 2022 8,207,001 $ 405,188 $ 13,222 $ 47,901 $</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" s="5" t="n">
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" s="5" t="n">
         <v>0.268828</v>
       </c>
-      <c r="F108" s="5" t="n">
+      <c r="F225" s="5" t="n">
         <v>-0.197483</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
         <is>
           <t>-</t>
         </is>
